--- a/PaloAlto_FW/decomm_rule/rules_to_decommission.xlsx
+++ b/PaloAlto_FW/decomm_rule/rules_to_decommission.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tompet/Documents/git/misc/PaloAlto_FW/decomm_rule/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{029E3052-1088-8445-A469-52CF7408ABEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{B0A9AE7C-3C97-CD4D-A71D-7D41A3C1961A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="680" yWindow="760" windowWidth="28040" windowHeight="17240" xr2:uid="{B5E47F3F-D749-874F-819B-A0F46652D612}"/>
+    <workbookView xWindow="680" yWindow="760" windowWidth="28040" windowHeight="16960" xr2:uid="{B5E47F3F-D749-874F-819B-A0F46652D612}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,10 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="44">
   <si>
     <t>vsys</t>
   </si>
@@ -69,13 +66,115 @@
   </si>
   <si>
     <t>ab</t>
+  </si>
+  <si>
+    <t>rule3</t>
+  </si>
+  <si>
+    <t>rule4</t>
+  </si>
+  <si>
+    <t>rule5</t>
+  </si>
+  <si>
+    <t>rule6</t>
+  </si>
+  <si>
+    <t>rule7</t>
+  </si>
+  <si>
+    <t>rule8</t>
+  </si>
+  <si>
+    <t>rule9</t>
+  </si>
+  <si>
+    <t>rule10</t>
+  </si>
+  <si>
+    <t>rule11</t>
+  </si>
+  <si>
+    <t>rule12</t>
+  </si>
+  <si>
+    <t>rule13</t>
+  </si>
+  <si>
+    <t>rule14</t>
+  </si>
+  <si>
+    <t>rule15</t>
+  </si>
+  <si>
+    <t>rule16</t>
+  </si>
+  <si>
+    <t>rule17</t>
+  </si>
+  <si>
+    <t>rule18</t>
+  </si>
+  <si>
+    <t>rule19</t>
+  </si>
+  <si>
+    <t>RFC1111112</t>
+  </si>
+  <si>
+    <t>RFC1111113</t>
+  </si>
+  <si>
+    <t>RFC1111114</t>
+  </si>
+  <si>
+    <t>RFC1111115</t>
+  </si>
+  <si>
+    <t>RFC1111116</t>
+  </si>
+  <si>
+    <t>RFC1111117</t>
+  </si>
+  <si>
+    <t>RFC1111118</t>
+  </si>
+  <si>
+    <t>RFC1111119</t>
+  </si>
+  <si>
+    <t>RFC1111120</t>
+  </si>
+  <si>
+    <t>RFC1111121</t>
+  </si>
+  <si>
+    <t>RFC1111122</t>
+  </si>
+  <si>
+    <t>RFC1111123</t>
+  </si>
+  <si>
+    <t>RFC1111124</t>
+  </si>
+  <si>
+    <t>RFC1111125</t>
+  </si>
+  <si>
+    <t>RFC1111126</t>
+  </si>
+  <si>
+    <t>RFC1111127</t>
+  </si>
+  <si>
+    <t>RFC1111128</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -88,6 +187,12 @@
       <color rgb="FFCE9178"/>
       <name val="Menlo"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -447,7 +552,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E975B015-9DB6-0043-8C41-C90A035BAE35}">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.1640625" customWidth="1"/>
@@ -456,54 +561,288 @@
     <col min="4" max="4" width="18.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
       <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="G8" t="s">
-        <v>0</v>
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" t="s">
+        <v>40</v>
+      </c>
+      <c r="D17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" t="s">
+        <v>41</v>
+      </c>
+      <c r="D18" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" t="s">
+        <v>42</v>
+      </c>
+      <c r="D19" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" t="s">
+        <v>43</v>
+      </c>
+      <c r="D20" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/PaloAlto_FW/decomm_rule/rules_to_decommission.xlsx
+++ b/PaloAlto_FW/decomm_rule/rules_to_decommission.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tompet/Documents/git/misc/PaloAlto_FW/decomm_rule/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{B0A9AE7C-3C97-CD4D-A71D-7D41A3C1961A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{1799DD7B-BD70-8A42-9FCC-D91B13B0A6E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="680" yWindow="760" windowWidth="28040" windowHeight="16960" xr2:uid="{B5E47F3F-D749-874F-819B-A0F46652D612}"/>
+    <workbookView xWindow="1360" yWindow="800" windowWidth="28040" windowHeight="16960" xr2:uid="{B5E47F3F-D749-874F-819B-A0F46652D612}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="46">
   <si>
     <t>vsys</t>
   </si>
@@ -62,12 +62,6 @@
     <t>rule2</t>
   </si>
   <si>
-    <t>RFC1111111</t>
-  </si>
-  <si>
-    <t>ab</t>
-  </si>
-  <si>
     <t>rule3</t>
   </si>
   <si>
@@ -119,55 +113,67 @@
     <t>rule19</t>
   </si>
   <si>
-    <t>RFC1111112</t>
-  </si>
-  <si>
-    <t>RFC1111113</t>
-  </si>
-  <si>
-    <t>RFC1111114</t>
-  </si>
-  <si>
-    <t>RFC1111115</t>
-  </si>
-  <si>
-    <t>RFC1111116</t>
-  </si>
-  <si>
-    <t>RFC1111117</t>
-  </si>
-  <si>
-    <t>RFC1111118</t>
-  </si>
-  <si>
-    <t>RFC1111119</t>
-  </si>
-  <si>
-    <t>RFC1111120</t>
-  </si>
-  <si>
-    <t>RFC1111121</t>
-  </si>
-  <si>
-    <t>RFC1111122</t>
-  </si>
-  <si>
-    <t>RFC1111123</t>
-  </si>
-  <si>
-    <t>RFC1111124</t>
-  </si>
-  <si>
-    <t>RFC1111125</t>
-  </si>
-  <si>
-    <t>RFC1111126</t>
-  </si>
-  <si>
-    <t>RFC1111127</t>
-  </si>
-  <si>
-    <t>RFC1111128</t>
+    <t>CHC1111111</t>
+  </si>
+  <si>
+    <t>CHC1111112</t>
+  </si>
+  <si>
+    <t>CHC1111113</t>
+  </si>
+  <si>
+    <t>CHC1111114</t>
+  </si>
+  <si>
+    <t>CHC1111115</t>
+  </si>
+  <si>
+    <t>CHC1111116</t>
+  </si>
+  <si>
+    <t>CHC1111117</t>
+  </si>
+  <si>
+    <t>CHC1111118</t>
+  </si>
+  <si>
+    <t>CHC1111119</t>
+  </si>
+  <si>
+    <t>CHC1111120</t>
+  </si>
+  <si>
+    <t>CHC1111121</t>
+  </si>
+  <si>
+    <t>CHC1111122</t>
+  </si>
+  <si>
+    <t>CHC1111123</t>
+  </si>
+  <si>
+    <t>CHC1111124</t>
+  </si>
+  <si>
+    <t>CHC1111125</t>
+  </si>
+  <si>
+    <t>CHC1111126</t>
+  </si>
+  <si>
+    <t>CHC1111127</t>
+  </si>
+  <si>
+    <t>CHC1111128</t>
+  </si>
+  <si>
+    <t>CHC1111129</t>
+  </si>
+  <si>
+    <t>artur</t>
+  </si>
+  <si>
+    <t>ecomm</t>
   </si>
 </sst>
 </file>
@@ -583,10 +589,10 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -597,10 +603,10 @@
         <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -608,13 +614,13 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
         <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -622,13 +628,13 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
         <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -636,13 +642,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C6" t="s">
         <v>29</v>
       </c>
       <c r="D6" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -650,13 +656,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
         <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -664,13 +670,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C8" t="s">
         <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -678,13 +684,13 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
         <v>32</v>
       </c>
       <c r="D9" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -692,13 +698,13 @@
         <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
         <v>33</v>
       </c>
       <c r="D10" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
@@ -706,139 +712,139 @@
         <v>5</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s">
         <v>34</v>
       </c>
       <c r="D11" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C12" t="s">
         <v>35</v>
       </c>
       <c r="D12" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C13" t="s">
         <v>36</v>
       </c>
       <c r="D13" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C14" t="s">
         <v>37</v>
       </c>
       <c r="D14" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C15" t="s">
         <v>38</v>
       </c>
       <c r="D15" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="B16" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C16" t="s">
         <v>39</v>
       </c>
       <c r="D16" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C17" t="s">
         <v>40</v>
       </c>
       <c r="D17" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C18" t="s">
         <v>41</v>
       </c>
       <c r="D18" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="B19" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C19" t="s">
         <v>42</v>
       </c>
       <c r="D19" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C20" t="s">
         <v>43</v>
       </c>
       <c r="D20" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
